--- a/artfynd/A 13867-2020 artfynd.xlsx
+++ b/artfynd/A 13867-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13867-2020 artfynd.xlsx
+++ b/artfynd/A 13867-2020 artfynd.xlsx
@@ -2461,10 +2461,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119788796</v>
+        <v>119788820</v>
       </c>
       <c r="B18" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2473,25 +2473,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2501,10 +2501,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>808694</v>
+        <v>808645</v>
       </c>
       <c r="R18" t="n">
-        <v>7257299</v>
+        <v>7257284</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2567,10 +2567,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119788792</v>
+        <v>119788822</v>
       </c>
       <c r="B19" t="n">
-        <v>87406</v>
+        <v>97907</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2579,25 +2579,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2607,10 +2607,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>808711</v>
+        <v>808549</v>
       </c>
       <c r="R19" t="n">
-        <v>7257289</v>
+        <v>7257324</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2673,10 +2673,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119788806</v>
+        <v>119788824</v>
       </c>
       <c r="B20" t="n">
-        <v>91832</v>
+        <v>90580</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2689,21 +2689,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4361</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>808673</v>
+        <v>808649</v>
       </c>
       <c r="R20" t="n">
-        <v>7257303</v>
+        <v>7257223</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119788810</v>
+        <v>119788796</v>
       </c>
       <c r="B22" t="n">
-        <v>79607</v>
+        <v>90562</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2901,21 +2901,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2925,10 +2925,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>808606</v>
+        <v>808694</v>
       </c>
       <c r="R22" t="n">
-        <v>7257314</v>
+        <v>7257299</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2991,7 +2991,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119788821</v>
+        <v>119788816</v>
       </c>
       <c r="B23" t="n">
         <v>97907</v>
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>808635</v>
+        <v>808711</v>
       </c>
       <c r="R23" t="n">
-        <v>7257285</v>
+        <v>7257289</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3097,10 +3097,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119788824</v>
+        <v>119788810</v>
       </c>
       <c r="B24" t="n">
-        <v>90580</v>
+        <v>79607</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3113,21 +3113,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3137,10 +3137,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>808649</v>
+        <v>808606</v>
       </c>
       <c r="R24" t="n">
-        <v>7257223</v>
+        <v>7257314</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3203,10 +3203,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119788823</v>
+        <v>119788806</v>
       </c>
       <c r="B25" t="n">
-        <v>97907</v>
+        <v>91832</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3215,25 +3215,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>808462</v>
+        <v>808673</v>
       </c>
       <c r="R25" t="n">
-        <v>7257364</v>
+        <v>7257303</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3309,7 +3309,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119788816</v>
+        <v>119788821</v>
       </c>
       <c r="B26" t="n">
         <v>97907</v>
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>808711</v>
+        <v>808635</v>
       </c>
       <c r="R26" t="n">
-        <v>7257289</v>
+        <v>7257285</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3415,10 +3415,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119788822</v>
+        <v>119788792</v>
       </c>
       <c r="B27" t="n">
-        <v>97907</v>
+        <v>87406</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3427,25 +3427,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>4412</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>808549</v>
+        <v>808711</v>
       </c>
       <c r="R27" t="n">
-        <v>7257324</v>
+        <v>7257289</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119788820</v>
+        <v>119788795</v>
       </c>
       <c r="B28" t="n">
-        <v>97907</v>
+        <v>87406</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3533,25 +3533,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>4412</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3561,10 +3561,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>808645</v>
+        <v>808639</v>
       </c>
       <c r="R28" t="n">
-        <v>7257284</v>
+        <v>7257288</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3627,10 +3627,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119788795</v>
+        <v>119788826</v>
       </c>
       <c r="B29" t="n">
-        <v>87406</v>
+        <v>78526</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3643,21 +3643,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4412</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>808639</v>
+        <v>808683</v>
       </c>
       <c r="R29" t="n">
-        <v>7257288</v>
+        <v>7257302</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3733,10 +3733,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119788826</v>
+        <v>119788823</v>
       </c>
       <c r="B30" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3745,25 +3745,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>808683</v>
+        <v>808462</v>
       </c>
       <c r="R30" t="n">
-        <v>7257302</v>
+        <v>7257364</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 13867-2020 artfynd.xlsx
+++ b/artfynd/A 13867-2020 artfynd.xlsx
@@ -2461,7 +2461,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119788820</v>
+        <v>119788817</v>
       </c>
       <c r="B18" t="n">
         <v>97907</v>
@@ -2501,10 +2501,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>808645</v>
+        <v>808692</v>
       </c>
       <c r="R18" t="n">
-        <v>7257284</v>
+        <v>7257265</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2567,10 +2567,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119788822</v>
+        <v>119788810</v>
       </c>
       <c r="B19" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2579,25 +2579,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2607,10 +2607,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>808549</v>
+        <v>808606</v>
       </c>
       <c r="R19" t="n">
-        <v>7257324</v>
+        <v>7257314</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2673,10 +2673,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119788824</v>
+        <v>119788821</v>
       </c>
       <c r="B20" t="n">
-        <v>90580</v>
+        <v>97907</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2685,25 +2685,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>808649</v>
+        <v>808635</v>
       </c>
       <c r="R20" t="n">
-        <v>7257223</v>
+        <v>7257285</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2779,7 +2779,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119788817</v>
+        <v>119788823</v>
       </c>
       <c r="B21" t="n">
         <v>97907</v>
@@ -2819,10 +2819,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>808692</v>
+        <v>808462</v>
       </c>
       <c r="R21" t="n">
-        <v>7257265</v>
+        <v>7257364</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119788796</v>
+        <v>119788824</v>
       </c>
       <c r="B22" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2901,21 +2901,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2925,10 +2925,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>808694</v>
+        <v>808649</v>
       </c>
       <c r="R22" t="n">
-        <v>7257299</v>
+        <v>7257223</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2991,10 +2991,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119788816</v>
+        <v>119788826</v>
       </c>
       <c r="B23" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3003,25 +3003,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>808711</v>
+        <v>808683</v>
       </c>
       <c r="R23" t="n">
-        <v>7257289</v>
+        <v>7257302</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3097,10 +3097,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119788810</v>
+        <v>119788795</v>
       </c>
       <c r="B24" t="n">
-        <v>79607</v>
+        <v>87406</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3113,21 +3113,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>4412</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3137,10 +3137,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>808606</v>
+        <v>808639</v>
       </c>
       <c r="R24" t="n">
-        <v>7257314</v>
+        <v>7257288</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3203,10 +3203,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119788806</v>
+        <v>119788796</v>
       </c>
       <c r="B25" t="n">
-        <v>91832</v>
+        <v>90562</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3219,21 +3219,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>808673</v>
+        <v>808694</v>
       </c>
       <c r="R25" t="n">
-        <v>7257303</v>
+        <v>7257299</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3309,7 +3309,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119788821</v>
+        <v>119788822</v>
       </c>
       <c r="B26" t="n">
         <v>97907</v>
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>808635</v>
+        <v>808549</v>
       </c>
       <c r="R26" t="n">
-        <v>7257285</v>
+        <v>7257324</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3415,10 +3415,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119788792</v>
+        <v>119788820</v>
       </c>
       <c r="B27" t="n">
-        <v>87406</v>
+        <v>97907</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3427,25 +3427,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>808711</v>
+        <v>808645</v>
       </c>
       <c r="R27" t="n">
-        <v>7257289</v>
+        <v>7257284</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3521,7 +3521,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119788795</v>
+        <v>119788792</v>
       </c>
       <c r="B28" t="n">
         <v>87406</v>
@@ -3561,10 +3561,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>808639</v>
+        <v>808711</v>
       </c>
       <c r="R28" t="n">
-        <v>7257288</v>
+        <v>7257289</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3627,10 +3627,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119788826</v>
+        <v>119788816</v>
       </c>
       <c r="B29" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3639,25 +3639,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>808683</v>
+        <v>808711</v>
       </c>
       <c r="R29" t="n">
-        <v>7257302</v>
+        <v>7257289</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3733,10 +3733,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119788823</v>
+        <v>119788806</v>
       </c>
       <c r="B30" t="n">
-        <v>97907</v>
+        <v>91832</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3745,25 +3745,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>808462</v>
+        <v>808673</v>
       </c>
       <c r="R30" t="n">
-        <v>7257364</v>
+        <v>7257303</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 13867-2020 artfynd.xlsx
+++ b/artfynd/A 13867-2020 artfynd.xlsx
@@ -2249,10 +2249,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119745803</v>
+        <v>119745791</v>
       </c>
       <c r="B16" t="n">
-        <v>91852</v>
+        <v>87406</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2261,25 +2261,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4366</v>
+        <v>4412</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>808645</v>
+        <v>808613</v>
       </c>
       <c r="R16" t="n">
-        <v>7257243</v>
+        <v>7257227</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2355,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119745791</v>
+        <v>119745803</v>
       </c>
       <c r="B17" t="n">
-        <v>87406</v>
+        <v>91852</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2367,25 +2367,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4412</v>
+        <v>4366</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>808613</v>
+        <v>808645</v>
       </c>
       <c r="R17" t="n">
-        <v>7257227</v>
+        <v>7257243</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2461,10 +2461,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119788817</v>
+        <v>119788826</v>
       </c>
       <c r="B18" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2473,25 +2473,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2501,10 +2501,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>808692</v>
+        <v>808683</v>
       </c>
       <c r="R18" t="n">
-        <v>7257265</v>
+        <v>7257302</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2567,10 +2567,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119788810</v>
+        <v>119788823</v>
       </c>
       <c r="B19" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2579,25 +2579,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2607,10 +2607,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>808606</v>
+        <v>808462</v>
       </c>
       <c r="R19" t="n">
-        <v>7257314</v>
+        <v>7257364</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2673,7 +2673,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119788821</v>
+        <v>119788822</v>
       </c>
       <c r="B20" t="n">
         <v>97907</v>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>808635</v>
+        <v>808549</v>
       </c>
       <c r="R20" t="n">
-        <v>7257285</v>
+        <v>7257324</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2779,7 +2779,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119788823</v>
+        <v>119788817</v>
       </c>
       <c r="B21" t="n">
         <v>97907</v>
@@ -2819,10 +2819,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>808462</v>
+        <v>808692</v>
       </c>
       <c r="R21" t="n">
-        <v>7257364</v>
+        <v>7257265</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119788824</v>
+        <v>119788816</v>
       </c>
       <c r="B22" t="n">
-        <v>90580</v>
+        <v>97907</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2897,25 +2897,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2925,10 +2925,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>808649</v>
+        <v>808711</v>
       </c>
       <c r="R22" t="n">
-        <v>7257223</v>
+        <v>7257289</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2991,10 +2991,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119788826</v>
+        <v>119788810</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3007,21 +3007,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>808683</v>
+        <v>808606</v>
       </c>
       <c r="R23" t="n">
-        <v>7257302</v>
+        <v>7257314</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3097,10 +3097,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119788795</v>
+        <v>119788824</v>
       </c>
       <c r="B24" t="n">
-        <v>87406</v>
+        <v>90580</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3113,21 +3113,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4412</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3137,10 +3137,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>808639</v>
+        <v>808649</v>
       </c>
       <c r="R24" t="n">
-        <v>7257288</v>
+        <v>7257223</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3309,10 +3309,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119788822</v>
+        <v>119788792</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>87406</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3321,25 +3321,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>4412</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>808549</v>
+        <v>808711</v>
       </c>
       <c r="R26" t="n">
-        <v>7257324</v>
+        <v>7257289</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3415,10 +3415,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119788820</v>
+        <v>119788795</v>
       </c>
       <c r="B27" t="n">
-        <v>97907</v>
+        <v>87406</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3427,25 +3427,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>4412</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>808645</v>
+        <v>808639</v>
       </c>
       <c r="R27" t="n">
-        <v>7257284</v>
+        <v>7257288</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119788792</v>
+        <v>119788821</v>
       </c>
       <c r="B28" t="n">
-        <v>87406</v>
+        <v>97907</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3533,25 +3533,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3561,10 +3561,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>808711</v>
+        <v>808635</v>
       </c>
       <c r="R28" t="n">
-        <v>7257289</v>
+        <v>7257285</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3627,7 +3627,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119788816</v>
+        <v>119788820</v>
       </c>
       <c r="B29" t="n">
         <v>97907</v>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>808711</v>
+        <v>808645</v>
       </c>
       <c r="R29" t="n">
-        <v>7257289</v>
+        <v>7257284</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 13867-2020 artfynd.xlsx
+++ b/artfynd/A 13867-2020 artfynd.xlsx
@@ -2141,7 +2141,7 @@
         <v>119709349</v>
       </c>
       <c r="B15" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>119745791</v>
       </c>
       <c r="B16" t="n">
-        <v>87406</v>
+        <v>87423</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>119745803</v>
       </c>
       <c r="B17" t="n">
-        <v>91852</v>
+        <v>91870</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2461,10 +2461,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119788826</v>
+        <v>119788821</v>
       </c>
       <c r="B18" t="n">
-        <v>78526</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2473,25 +2473,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2501,10 +2501,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>808683</v>
+        <v>808635</v>
       </c>
       <c r="R18" t="n">
-        <v>7257302</v>
+        <v>7257285</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2570,7 +2570,7 @@
         <v>119788823</v>
       </c>
       <c r="B19" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2673,10 +2673,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119788822</v>
+        <v>119788810</v>
       </c>
       <c r="B20" t="n">
-        <v>97907</v>
+        <v>79623</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2685,25 +2685,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>808549</v>
+        <v>808606</v>
       </c>
       <c r="R20" t="n">
-        <v>7257324</v>
+        <v>7257314</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2779,10 +2779,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119788817</v>
+        <v>119788796</v>
       </c>
       <c r="B21" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2791,25 +2791,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2819,10 +2819,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>808692</v>
+        <v>808694</v>
       </c>
       <c r="R21" t="n">
-        <v>7257265</v>
+        <v>7257299</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119788816</v>
+        <v>119788822</v>
       </c>
       <c r="B22" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2925,10 +2925,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>808711</v>
+        <v>808549</v>
       </c>
       <c r="R22" t="n">
-        <v>7257289</v>
+        <v>7257324</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2991,10 +2991,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119788810</v>
+        <v>119788816</v>
       </c>
       <c r="B23" t="n">
-        <v>79607</v>
+        <v>97930</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3003,25 +3003,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>808606</v>
+        <v>808711</v>
       </c>
       <c r="R23" t="n">
-        <v>7257314</v>
+        <v>7257289</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3097,10 +3097,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119788824</v>
+        <v>119788792</v>
       </c>
       <c r="B24" t="n">
-        <v>90580</v>
+        <v>87423</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3113,21 +3113,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>4412</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3137,10 +3137,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>808649</v>
+        <v>808711</v>
       </c>
       <c r="R24" t="n">
-        <v>7257223</v>
+        <v>7257289</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3203,10 +3203,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119788796</v>
+        <v>119788795</v>
       </c>
       <c r="B25" t="n">
-        <v>90562</v>
+        <v>87423</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3219,21 +3219,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>4412</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>808694</v>
+        <v>808639</v>
       </c>
       <c r="R25" t="n">
-        <v>7257299</v>
+        <v>7257288</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3309,10 +3309,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119788792</v>
+        <v>119788820</v>
       </c>
       <c r="B26" t="n">
-        <v>87406</v>
+        <v>97930</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3321,25 +3321,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>808711</v>
+        <v>808645</v>
       </c>
       <c r="R26" t="n">
-        <v>7257289</v>
+        <v>7257284</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3415,10 +3415,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119788795</v>
+        <v>119788824</v>
       </c>
       <c r="B27" t="n">
-        <v>87406</v>
+        <v>90598</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3431,21 +3431,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4412</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>808639</v>
+        <v>808649</v>
       </c>
       <c r="R27" t="n">
-        <v>7257288</v>
+        <v>7257223</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119788821</v>
+        <v>119788806</v>
       </c>
       <c r="B28" t="n">
-        <v>97907</v>
+        <v>91850</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3533,25 +3533,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3561,10 +3561,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>808635</v>
+        <v>808673</v>
       </c>
       <c r="R28" t="n">
-        <v>7257285</v>
+        <v>7257303</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3627,10 +3627,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119788820</v>
+        <v>119788826</v>
       </c>
       <c r="B29" t="n">
-        <v>97907</v>
+        <v>78542</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3639,25 +3639,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>808645</v>
+        <v>808683</v>
       </c>
       <c r="R29" t="n">
-        <v>7257284</v>
+        <v>7257302</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3733,10 +3733,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119788806</v>
+        <v>119788817</v>
       </c>
       <c r="B30" t="n">
-        <v>91832</v>
+        <v>97930</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3745,25 +3745,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>808673</v>
+        <v>808692</v>
       </c>
       <c r="R30" t="n">
-        <v>7257303</v>
+        <v>7257265</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3842,7 +3842,7 @@
         <v>119788829</v>
       </c>
       <c r="B31" t="n">
-        <v>91861</v>
+        <v>91879</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 13867-2020 artfynd.xlsx
+++ b/artfynd/A 13867-2020 artfynd.xlsx
@@ -2461,10 +2461,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119788821</v>
+        <v>119788792</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
+        <v>87423</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2473,25 +2473,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>4412</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2501,10 +2501,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>808635</v>
+        <v>808711</v>
       </c>
       <c r="R18" t="n">
-        <v>7257285</v>
+        <v>7257289</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2567,10 +2567,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119788823</v>
+        <v>119788795</v>
       </c>
       <c r="B19" t="n">
-        <v>97930</v>
+        <v>87423</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2579,25 +2579,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>4412</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2607,10 +2607,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>808462</v>
+        <v>808639</v>
       </c>
       <c r="R19" t="n">
-        <v>7257364</v>
+        <v>7257288</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2673,10 +2673,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119788810</v>
+        <v>119788820</v>
       </c>
       <c r="B20" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2685,25 +2685,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>808606</v>
+        <v>808645</v>
       </c>
       <c r="R20" t="n">
-        <v>7257314</v>
+        <v>7257284</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2779,10 +2779,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119788796</v>
+        <v>119788824</v>
       </c>
       <c r="B21" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2795,21 +2795,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2819,10 +2819,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>808694</v>
+        <v>808649</v>
       </c>
       <c r="R21" t="n">
-        <v>7257299</v>
+        <v>7257223</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119788822</v>
+        <v>119788826</v>
       </c>
       <c r="B22" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2897,25 +2897,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2925,10 +2925,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>808549</v>
+        <v>808683</v>
       </c>
       <c r="R22" t="n">
-        <v>7257324</v>
+        <v>7257302</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2991,7 +2991,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119788816</v>
+        <v>119788821</v>
       </c>
       <c r="B23" t="n">
         <v>97930</v>
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>808711</v>
+        <v>808635</v>
       </c>
       <c r="R23" t="n">
-        <v>7257289</v>
+        <v>7257285</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3097,10 +3097,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119788792</v>
+        <v>119788806</v>
       </c>
       <c r="B24" t="n">
-        <v>87423</v>
+        <v>91850</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3113,21 +3113,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4412</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3137,10 +3137,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>808711</v>
+        <v>808673</v>
       </c>
       <c r="R24" t="n">
-        <v>7257289</v>
+        <v>7257303</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3203,10 +3203,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119788795</v>
+        <v>119788822</v>
       </c>
       <c r="B25" t="n">
-        <v>87423</v>
+        <v>97930</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3215,25 +3215,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>808639</v>
+        <v>808549</v>
       </c>
       <c r="R25" t="n">
-        <v>7257288</v>
+        <v>7257324</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3309,7 +3309,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119788820</v>
+        <v>119788823</v>
       </c>
       <c r="B26" t="n">
         <v>97930</v>
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>808645</v>
+        <v>808462</v>
       </c>
       <c r="R26" t="n">
-        <v>7257284</v>
+        <v>7257364</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3415,10 +3415,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119788824</v>
+        <v>119788810</v>
       </c>
       <c r="B27" t="n">
-        <v>90598</v>
+        <v>79623</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3431,21 +3431,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>808649</v>
+        <v>808606</v>
       </c>
       <c r="R27" t="n">
-        <v>7257223</v>
+        <v>7257314</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119788806</v>
+        <v>119788817</v>
       </c>
       <c r="B28" t="n">
-        <v>91850</v>
+        <v>97930</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3533,25 +3533,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3561,10 +3561,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>808673</v>
+        <v>808692</v>
       </c>
       <c r="R28" t="n">
-        <v>7257303</v>
+        <v>7257265</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3627,10 +3627,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119788826</v>
+        <v>119788816</v>
       </c>
       <c r="B29" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3639,25 +3639,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>808683</v>
+        <v>808711</v>
       </c>
       <c r="R29" t="n">
-        <v>7257302</v>
+        <v>7257289</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3733,10 +3733,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119788817</v>
+        <v>119788796</v>
       </c>
       <c r="B30" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3745,25 +3745,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>808692</v>
+        <v>808694</v>
       </c>
       <c r="R30" t="n">
-        <v>7257265</v>
+        <v>7257299</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
